--- a/2914.T.xlsx
+++ b/2914.T.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1304D4-A191-4C4A-B6C3-D85E0D10BF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C734A10-839A-4816-9527-C0D445C1FA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{60080457-8EED-45E9-99AC-39ADD7222A04}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="101">
   <si>
     <t>Price</t>
   </si>
@@ -332,6 +332,15 @@
   <si>
     <t>in mio YEN</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
+  <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>Masamichi Terabatake</t>
+  </si>
 </sst>
 </file>
 
@@ -341,13 +350,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -542,41 +557,45 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -600,16 +619,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -624,8 +643,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="10598150" y="152400"/>
-          <a:ext cx="19050" cy="5187950"/>
+          <a:off x="15125700" y="219075"/>
+          <a:ext cx="19050" cy="4381500"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -993,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="3">
-        <v>4744</v>
+        <v>5714</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -1002,10 +1021,10 @@
         <v>1</v>
       </c>
       <c r="J3" s="3">
-        <v>1775.6347480288</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>89</v>
+        <v>1775.404</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -1017,7 +1036,7 @@
       </c>
       <c r="J4" s="3">
         <f>J2*J3</f>
-        <v>8423611.2446486279</v>
+        <v>10144658.456</v>
       </c>
       <c r="K4" s="5"/>
     </row>
@@ -1026,10 +1045,11 @@
         <v>3</v>
       </c>
       <c r="J5" s="3">
-        <v>865185</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>89</v>
+        <f>252923+21000</f>
+        <v>273923</v>
+      </c>
+      <c r="K5" s="28" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -1044,11 +1064,11 @@
         <v>4</v>
       </c>
       <c r="J6" s="3">
-        <f>186479+1439954</f>
-        <v>1626433</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>89</v>
+        <f>559542+120000</f>
+        <v>679542</v>
+      </c>
+      <c r="K6" s="28" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -1064,7 +1084,7 @@
       </c>
       <c r="J7" s="3">
         <f>J4-J5+J6</f>
-        <v>9184859.2446486279</v>
+        <v>10550277.456</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -1084,6 +1104,12 @@
         <v>29</v>
       </c>
       <c r="F10" s="13"/>
+      <c r="I10" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" s="27" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
@@ -1192,7 +1218,8 @@
     <col min="15" max="15" width="9.140625" style="2"/>
     <col min="16" max="19" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="20" max="22" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="2"/>
+    <col min="23" max="23" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
@@ -1257,6 +1284,9 @@
       </c>
       <c r="V2" s="5" t="s">
         <v>24</v>
+      </c>
+      <c r="W2" s="28" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.2">
@@ -1429,9 +1459,11 @@
         <v>2591303</v>
       </c>
       <c r="V6" s="3">
-        <v>2747000</v>
-      </c>
-      <c r="W6" s="3"/>
+        <v>2896984</v>
+      </c>
+      <c r="W6" s="3">
+        <v>3305408</v>
+      </c>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
@@ -1483,9 +1515,11 @@
         <v>94875</v>
       </c>
       <c r="V7" s="3">
-        <v>93000</v>
-      </c>
-      <c r="W7" s="3"/>
+        <v>2541</v>
+      </c>
+      <c r="W7" s="3">
+        <v>2652</v>
+      </c>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
@@ -1537,9 +1571,11 @@
         <v>153885</v>
       </c>
       <c r="V8" s="3">
-        <v>156500</v>
-      </c>
-      <c r="W8" s="3"/>
+        <v>157183</v>
+      </c>
+      <c r="W8" s="3">
+        <v>149537</v>
+      </c>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
@@ -1591,9 +1627,11 @@
         <v>2841077</v>
       </c>
       <c r="V9" s="20">
-        <v>3109000</v>
-      </c>
-      <c r="W9" s="3"/>
+        <v>3056709</v>
+      </c>
+      <c r="W9" s="20">
+        <v>3467675</v>
+      </c>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
@@ -1634,8 +1672,12 @@
       <c r="U10" s="3">
         <v>1225947</v>
       </c>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
+      <c r="V10" s="3">
+        <v>1379284</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1519091</v>
+      </c>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
@@ -1710,8 +1752,14 @@
         <f>U9-U10</f>
         <v>1615130</v>
       </c>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
+      <c r="V11" s="3">
+        <f t="shared" ref="V11:W11" si="2">V9-V10</f>
+        <v>1677425</v>
+      </c>
+      <c r="W11" s="3">
+        <f t="shared" si="2"/>
+        <v>1948584</v>
+      </c>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
@@ -1756,8 +1804,14 @@
         <f>30027+8332</f>
         <v>38359</v>
       </c>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
+      <c r="V12" s="3">
+        <f>31136+12885</f>
+        <v>44021</v>
+      </c>
+      <c r="W12" s="3">
+        <f>83284+13332</f>
+        <v>96616</v>
+      </c>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
@@ -1798,8 +1852,12 @@
       <c r="U13" s="3">
         <v>981052</v>
       </c>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
+      <c r="V13" s="3">
+        <v>1407224</v>
+      </c>
+      <c r="W13" s="3">
+        <v>1178162</v>
+      </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
@@ -1833,27 +1891,27 @@
         <v>216800</v>
       </c>
       <c r="I14" s="3">
-        <f>+I11+I12-I13</f>
+        <f t="shared" ref="I14:N14" si="3">+I11+I12-I13</f>
         <v>823400</v>
       </c>
       <c r="J14" s="3">
-        <f>+J11+J12-J13</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K14" s="3">
-        <f>+K11+K12-K13</f>
+        <f t="shared" si="3"/>
         <v>248757</v>
       </c>
       <c r="L14" s="3">
-        <f>+L11+L12-L13</f>
+        <f t="shared" si="3"/>
         <v>907600</v>
       </c>
       <c r="M14" s="3">
-        <f>+M11+M12-M13</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N14" s="3">
-        <f>+N11+N12-N13</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O14" s="3"/>
@@ -1869,8 +1927,14 @@
         <f>U11+U12-U13</f>
         <v>672437</v>
       </c>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
+      <c r="V14" s="3">
+        <f t="shared" ref="V14:W14" si="4">V11+V12-V13</f>
+        <v>314222</v>
+      </c>
+      <c r="W14" s="3">
+        <f t="shared" si="4"/>
+        <v>867038</v>
+      </c>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
@@ -1915,8 +1979,14 @@
         <f>44414-95222</f>
         <v>-50808</v>
       </c>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
+      <c r="V15" s="3">
+        <f>69004-158895</f>
+        <v>-89891</v>
+      </c>
+      <c r="W15" s="3">
+        <f>67942-195194</f>
+        <v>-127252</v>
+      </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
@@ -1931,68 +2001,68 @@
         <v>51</v>
       </c>
       <c r="C16" s="3">
-        <f t="shared" ref="C16:S16" si="2">C14+C15</f>
+        <f t="shared" ref="C16:S16" si="5">C14+C15</f>
         <v>0</v>
       </c>
       <c r="D16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>207200</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>764200</v>
       </c>
       <c r="F16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>201267</v>
       </c>
       <c r="H16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>216800</v>
       </c>
       <c r="I16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>823400</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>226067</v>
       </c>
       <c r="L16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>907600</v>
       </c>
       <c r="M16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T16" s="3">
@@ -2003,8 +2073,14 @@
         <f>U14+U15</f>
         <v>621629</v>
       </c>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
+      <c r="V16" s="3">
+        <f t="shared" ref="V16:W16" si="6">V14+V15</f>
+        <v>224331</v>
+      </c>
+      <c r="W16" s="3">
+        <f t="shared" si="6"/>
+        <v>739786</v>
+      </c>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
@@ -2045,8 +2121,12 @@
       <c r="U17" s="3">
         <v>136292</v>
       </c>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
+      <c r="V17" s="3">
+        <v>50406</v>
+      </c>
+      <c r="W17" s="3">
+        <v>238711</v>
+      </c>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
@@ -2081,10 +2161,20 @@
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
+      <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
+        <f>-8669+3356</f>
+        <v>-5313</v>
+      </c>
+      <c r="W18" s="3">
+        <f>-12139+3039</f>
+        <v>-9100</v>
+      </c>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
@@ -2099,19 +2189,19 @@
         <v>53</v>
       </c>
       <c r="C19" s="3">
-        <f t="shared" ref="C19:F19" si="3">+C16-C17-C18</f>
+        <f t="shared" ref="C19:F19" si="7">+C16-C17-C18</f>
         <v>0</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>207200</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>764200</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G19" s="3">
@@ -2119,63 +2209,66 @@
         <v>157267</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" ref="H19:N19" si="4">+H16-H17-H18</f>
+        <f t="shared" ref="H19:N19" si="8">+H16-H17-H18</f>
         <v>216800</v>
       </c>
       <c r="I19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>823400</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>157478</v>
       </c>
       <c r="L19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>907600</v>
       </c>
       <c r="M19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3">
-        <f t="shared" ref="P19" si="5">+P16-P17-P18</f>
+        <f t="shared" ref="P19" si="9">+P16-P17-P18</f>
         <v>0</v>
       </c>
       <c r="Q19" s="3">
-        <f t="shared" ref="Q19" si="6">+Q16-Q17-Q18</f>
+        <f t="shared" ref="Q19" si="10">+Q16-Q17-Q18</f>
         <v>0</v>
       </c>
       <c r="R19" s="3">
-        <f t="shared" ref="R19" si="7">+R16-R17-R18</f>
+        <f t="shared" ref="R19" si="11">+R16-R17-R18</f>
         <v>0</v>
       </c>
       <c r="S19" s="3">
-        <f t="shared" ref="S19" si="8">+S16-S17-S18</f>
+        <f t="shared" ref="S19" si="12">+S16-S17-S18</f>
         <v>0</v>
       </c>
       <c r="T19" s="3">
-        <f t="shared" ref="T19" si="9">+T16-T17-T18</f>
+        <f t="shared" ref="T19" si="13">+T16-T17-T18</f>
         <v>444174</v>
       </c>
       <c r="U19" s="3">
-        <f t="shared" ref="U19" si="10">+U16-U17-U18</f>
+        <f t="shared" ref="U19" si="14">+U16-U17-U18</f>
         <v>485337</v>
       </c>
       <c r="V19" s="3">
-        <f t="shared" ref="V19" si="11">+V16-V17-V18</f>
-        <v>0</v>
-      </c>
-      <c r="W19" s="3"/>
+        <f t="shared" ref="V19:W19" si="15">+V16-V17-V18</f>
+        <v>179238</v>
+      </c>
+      <c r="W19" s="3">
+        <f t="shared" si="15"/>
+        <v>510175</v>
+      </c>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
@@ -2221,19 +2314,19 @@
         <v>54</v>
       </c>
       <c r="C21" s="25" t="e">
-        <f t="shared" ref="C21:F21" si="12">+C19/C22</f>
+        <f t="shared" ref="C21:F21" si="16">+C19/C22</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D21" s="25" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E21" s="25" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F21" s="25" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G21" s="25">
@@ -2241,31 +2334,31 @@
         <v>88.584338007290896</v>
       </c>
       <c r="H21" s="25" t="e">
-        <f t="shared" ref="H21:N21" si="13">+H19/H22</f>
+        <f t="shared" ref="H21:N21" si="17">+H19/H22</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I21" s="25" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J21" s="25" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K21" s="25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>88.691262432030953</v>
       </c>
       <c r="L21" s="25" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M21" s="25" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N21" s="25" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O21" s="25"/>
@@ -2279,8 +2372,14 @@
       <c r="U21" s="25">
         <v>271.69</v>
       </c>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
+      <c r="V21" s="3">
+        <f>+V19/V22</f>
+        <v>102.10030253333933</v>
+      </c>
+      <c r="W21" s="3">
+        <f t="shared" ref="W21" si="18">+W19/W22</f>
+        <v>287.35713110931368</v>
+      </c>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
@@ -2312,31 +2411,35 @@
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3" t="e">
-        <f t="shared" ref="P22:T22" si="14">P19/P21</f>
+        <f t="shared" ref="P22:T22" si="19">P19/P21</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q22" s="3" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R22" s="3" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S22" s="3" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T22" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>1780.6133493686111</v>
       </c>
       <c r="U22" s="3">
         <f>U19/U21</f>
         <v>1786.3631344547093</v>
       </c>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
+      <c r="V22" s="3">
+        <v>1755.509</v>
+      </c>
+      <c r="W22" s="3">
+        <v>1775.404</v>
+      </c>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
@@ -2394,53 +2497,59 @@
         <v>0.14034364261168375</v>
       </c>
       <c r="I24" s="21">
-        <f t="shared" ref="I24:N24" si="15">+I9/E9-1</f>
+        <f t="shared" ref="I24:N24" si="20">+I9/E9-1</f>
         <v>7.7466631771787586E-2</v>
       </c>
       <c r="J24" s="21" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K24" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>0.11703922424098345</v>
       </c>
       <c r="L24" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9.4021215043394335E-2</v>
       </c>
       <c r="M24" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>-1</v>
       </c>
       <c r="N24" s="21" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O24" s="20"/>
       <c r="P24" s="21"/>
       <c r="Q24" s="21" t="e">
-        <f t="shared" ref="Q24:T24" si="16">Q9/P9-1</f>
+        <f t="shared" ref="Q24:T24" si="21">Q9/P9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R24" s="21" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S24" s="21" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T24" s="21" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U24" s="21">
         <f>U9/T9-1</f>
         <v>6.8945290748248844E-2</v>
       </c>
-      <c r="V24" s="20"/>
-      <c r="W24" s="20"/>
+      <c r="V24" s="21">
+        <f t="shared" ref="V24:W24" si="22">V9/U9-1</f>
+        <v>7.5897978125900822E-2</v>
+      </c>
+      <c r="W24" s="21">
+        <f t="shared" si="22"/>
+        <v>0.13444721103644475</v>
+      </c>
       <c r="X24" s="20"/>
       <c r="Y24" s="20"/>
       <c r="Z24" s="20"/>
@@ -2456,76 +2565,82 @@
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="19">
-        <f t="shared" ref="D25:J25" si="17">D11/D9</f>
+        <f t="shared" ref="D25:J25" si="23">D11/D9</f>
         <v>1</v>
       </c>
       <c r="E25" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="F25" s="19" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G25" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.56762564953878858</v>
       </c>
       <c r="H25" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="I25" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="J25" s="19" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K25" s="19">
-        <f t="shared" ref="K25:N25" si="18">K11/K9</f>
+        <f t="shared" ref="K25:N25" si="24">K11/K9</f>
         <v>0.58135192948810188</v>
       </c>
       <c r="L25" s="19">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="M25" s="19" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N25" s="19" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O25" s="19"/>
       <c r="P25" s="19" t="e">
-        <f t="shared" ref="P25:T25" si="19">P11/P9</f>
+        <f t="shared" ref="P25:T25" si="25">P11/P9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q25" s="19" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R25" s="19" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S25" s="19" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T25" s="19">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>0.58951920211661235</v>
       </c>
       <c r="U25" s="19">
         <f>U11/U9</f>
         <v>0.56849215983938484</v>
       </c>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
+      <c r="V25" s="19">
+        <f t="shared" ref="V25:W25" si="26">V11/V9</f>
+        <v>0.54876829950119554</v>
+      </c>
+      <c r="W25" s="19">
+        <f t="shared" si="26"/>
+        <v>0.56192809303063296</v>
+      </c>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
@@ -2541,76 +2656,82 @@
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="19">
-        <f t="shared" ref="D26:J26" si="20">D14/D9</f>
+        <f t="shared" ref="D26:J26" si="27">D14/D9</f>
         <v>0.28481099656357389</v>
       </c>
       <c r="E26" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="F26" s="19" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G26" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0.29151611504552682</v>
       </c>
       <c r="H26" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0.26133076181292186</v>
       </c>
       <c r="I26" s="19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="J26" s="19" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K26" s="19">
-        <f t="shared" ref="K26:N26" si="21">K14/K9</f>
+        <f t="shared" ref="K26:N26" si="28">K14/K9</f>
         <v>0.30080134851949442</v>
       </c>
       <c r="L26" s="19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="M26" s="19" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N26" s="19" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O26" s="19"/>
       <c r="P26" s="19" t="e">
-        <f t="shared" ref="P26:T26" si="22">P14/P9</f>
+        <f t="shared" ref="P26:T26" si="29">P14/P9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q26" s="19" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R26" s="19" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S26" s="19" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T26" s="19">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0.24590568553618136</v>
       </c>
       <c r="U26" s="19">
         <f>U14/U9</f>
         <v>0.23668383503861387</v>
       </c>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
+      <c r="V26" s="19">
+        <f t="shared" ref="V26:W26" si="30">V14/V9</f>
+        <v>0.10279748579272675</v>
+      </c>
+      <c r="W26" s="19">
+        <f t="shared" si="30"/>
+        <v>0.25003438903588138</v>
+      </c>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
@@ -2626,76 +2747,82 @@
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="19">
-        <f t="shared" ref="D27:J27" si="23">D17/D16</f>
+        <f t="shared" ref="D27:J27" si="31">D17/D16</f>
         <v>0</v>
       </c>
       <c r="E27" s="19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="F27" s="19" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G27" s="19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>0.21612584278595101</v>
       </c>
       <c r="H27" s="19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="I27" s="19">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J27" s="19" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K27" s="19">
-        <f t="shared" ref="K27:N27" si="24">K17/K16</f>
+        <f t="shared" ref="K27:N27" si="32">K17/K16</f>
         <v>0.3001012974029823</v>
       </c>
       <c r="L27" s="19">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M27" s="19" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N27" s="19" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O27" s="19"/>
       <c r="P27" s="19" t="e">
-        <f t="shared" ref="P27:T27" si="25">P17/P16</f>
+        <f t="shared" ref="P27:T27" si="33">P17/P16</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q27" s="19" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R27" s="19" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S27" s="19" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T27" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>0.25154056526992119</v>
       </c>
       <c r="U27" s="19">
         <f>U17/U16</f>
         <v>0.21924974542693471</v>
       </c>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
+      <c r="V27" s="19">
+        <f t="shared" ref="V27:W27" si="34">V17/V16</f>
+        <v>0.22469475908367545</v>
+      </c>
+      <c r="W27" s="19">
+        <f t="shared" si="34"/>
+        <v>0.32267574677001187</v>
+      </c>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
@@ -2965,19 +3092,19 @@
       <c r="N35" s="24"/>
       <c r="O35" s="24"/>
       <c r="P35" s="24">
-        <f t="shared" ref="P35:S35" si="26">SUM(P29:P34)</f>
+        <f t="shared" ref="P35:S35" si="35">SUM(P29:P34)</f>
         <v>0</v>
       </c>
       <c r="Q35" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="R35" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="S35" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T35" s="24">
@@ -3321,23 +3448,23 @@
       <c r="N44" s="24"/>
       <c r="O44" s="24"/>
       <c r="P44" s="24">
-        <f t="shared" ref="P44:T44" si="27">SUM(P36:P43)</f>
+        <f t="shared" ref="P44:T44" si="36">SUM(P36:P43)</f>
         <v>0</v>
       </c>
       <c r="Q44" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R44" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="S44" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="T44" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>3824500</v>
       </c>
       <c r="U44" s="24">
@@ -3373,27 +3500,27 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="20">
-        <f>P44+P35</f>
+        <f t="shared" ref="P45:U45" si="37">P44+P35</f>
         <v>0</v>
       </c>
       <c r="Q45" s="20">
-        <f>Q44+Q35</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="R45" s="20">
-        <f>R44+R35</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="S45" s="20">
-        <f>S44+S35</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="T45" s="20">
-        <f>T44+T35</f>
+        <f t="shared" si="37"/>
         <v>6548100</v>
       </c>
       <c r="U45" s="20">
-        <f>U44+U35</f>
+        <f t="shared" si="37"/>
         <v>7282000</v>
       </c>
       <c r="V45" s="3"/>
@@ -3653,23 +3780,23 @@
       <c r="N52" s="24"/>
       <c r="O52" s="24"/>
       <c r="P52" s="24">
-        <f t="shared" ref="P52:T52" si="28">SUM(P46:P51)</f>
+        <f t="shared" ref="P52:T52" si="38">SUM(P46:P51)</f>
         <v>0</v>
       </c>
       <c r="Q52" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="R52" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="S52" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="T52" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>1562700</v>
       </c>
       <c r="U52" s="24">
@@ -3933,23 +4060,23 @@
       <c r="N59" s="24"/>
       <c r="O59" s="24"/>
       <c r="P59" s="24">
-        <f t="shared" ref="P59:T59" si="29">SUM(P53:P58)</f>
+        <f t="shared" ref="P59:T59" si="39">SUM(P53:P58)</f>
         <v>0</v>
       </c>
       <c r="Q59" s="24">
-        <f t="shared" si="29"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="R59" s="24">
-        <f t="shared" si="29"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="S59" s="24">
-        <f t="shared" si="29"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T59" s="24">
-        <f t="shared" si="29"/>
+        <f t="shared" si="39"/>
         <v>1368600</v>
       </c>
       <c r="U59" s="24">
@@ -3985,23 +4112,23 @@
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
       <c r="P60" s="20">
-        <f t="shared" ref="P60:T60" si="30">P59+P52</f>
+        <f t="shared" ref="P60:T60" si="40">P59+P52</f>
         <v>0</v>
       </c>
       <c r="Q60" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="R60" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="S60" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="T60" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>2931300</v>
       </c>
       <c r="U60" s="20">
@@ -4075,27 +4202,27 @@
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
       <c r="P62" s="20">
-        <f>P60+P61</f>
+        <f t="shared" ref="P62:U62" si="41">P60+P61</f>
         <v>0</v>
       </c>
       <c r="Q62" s="20">
-        <f>Q60+Q61</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="R62" s="20">
-        <f>R60+R61</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="S62" s="20">
-        <f>S60+S61</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="T62" s="20">
-        <f>T60+T61</f>
+        <f t="shared" si="41"/>
         <v>6548100</v>
       </c>
       <c r="U62" s="20">
-        <f>U60+U61</f>
+        <f t="shared" si="41"/>
         <v>7282000</v>
       </c>
       <c r="V62" s="3"/>
@@ -4189,19 +4316,19 @@
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
       <c r="P65" s="3">
-        <f t="shared" ref="P65:S65" si="31">P14</f>
+        <f t="shared" ref="P65:S65" si="42">P14</f>
         <v>0</v>
       </c>
       <c r="Q65" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="R65" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="S65" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="T65" s="3">
